--- a/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún tipo de agresión</t>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,12 +572,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,52</t>
+          <t>0,37; 3,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,9</t>
+          <t>0,27; 1,79</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,62</t>
+          <t>0,39; 3,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,86</t>
+          <t>0,35; 4,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,92</t>
+          <t>0,62; 2,86</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,05</t>
+          <t>0,6; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,53</t>
+          <t>0,32; 2,32</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,63</t>
+          <t>0,32; 1,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,35</t>
+          <t>0,64; 2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,76</t>
+          <t>0,64; 1,72</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1824</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2174</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>586; 5307</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2967</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>934; 6122</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3270</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5606</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>674; 6629</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>746; 8786</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2380; 10979</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3447</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1841; 12996</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1883; 13506</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9687</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2137; 10110</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4904; 18281</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9056; 24495</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,33</t>
+          <t>0,37; 3,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,79</t>
+          <t>0,29; 1,91</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,84</t>
+          <t>0,41; 3,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,15</t>
+          <t>0,36; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,86</t>
+          <t>0,65; 2,99</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,25</t>
+          <t>0,67; 4,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,32</t>
+          <t>0,43; 2,4</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,52</t>
+          <t>0,37; 1,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,4</t>
+          <t>0,63; 2,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,72</t>
+          <t>0,64; 1,71</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1824</t>
+          <t>0; 2187</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2174</t>
+          <t>0; 2280</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>586; 5307</t>
+          <t>589; 5418</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2967</t>
+          <t>0; 3133</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>934; 6122</t>
+          <t>994; 6515</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>674; 6629</t>
+          <t>706; 6845</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>746; 8786</t>
+          <t>760; 8546</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2380; 10979</t>
+          <t>2515; 11474</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3447</t>
+          <t>0; 3746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1841; 12996</t>
+          <t>2051; 14388</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1883; 13506</t>
+          <t>2515; 13938</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2137; 10110</t>
+          <t>2489; 10120</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4904; 18281</t>
+          <t>4791; 17811</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9056; 24495</t>
+          <t>9123; 24445</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,4</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,39; 3,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,91</t>
+          <t>0,26; 2,01</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,96</t>
+          <t>0,34; 3,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,04</t>
+          <t>0,4; 3,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,99</t>
+          <t>0,62; 2,86</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,54; 3,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,71</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,4</t>
+          <t>0,45; 2,41</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,52</t>
+          <t>0,63; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,34</t>
+          <t>0,38; 1,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,71</t>
+          <t>0,68; 1,75</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>448</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>448</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2280</t>
+          <t>0; 2276</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>657</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2495</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>589; 5418</t>
+          <t>0; 2254</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3133</t>
+          <t>563; 5160</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>994; 6515</t>
+          <t>798; 6083</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5301</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>706; 6845</t>
+          <t>677; 7256</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>760; 8546</t>
+          <t>696; 6436</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2515; 11474</t>
+          <t>2321; 10667</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>766</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5845</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3746</t>
+          <t>1583; 11168</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2051; 14388</t>
+          <t>0; 4076</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2515; 13938</t>
+          <t>2483; 13233</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14089</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2489; 10120</t>
+          <t>4394; 16081</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4791; 17811</t>
+          <t>2419; 10719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9123; 24445</t>
+          <t>9040; 23271</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,71</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 3,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 2,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 3,64</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 3,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 2,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 3,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,59</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,45; 2,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 2,3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 1,71</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,68; 1,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.008603425799376075</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.00436676925295234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2453</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2276</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0.04708623423918468</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.02217743207051196</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.004171375116339294</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01263165206843914</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.008233951889027362</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2495</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.003872034212587768</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.00263382233164277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2254</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>563; 5160</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>798; 6083</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.01430792523623592</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.03546257922293165</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.02007286018475922</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.01455609142995729</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01377823846062455</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01419303559716709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2899</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2402</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5301</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.003397493406329965</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.003990821079585328</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.006214876876645081</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>677; 7256</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>696; 6436</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2321; 10667</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.0364315788932375</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.03692080817924596</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.02855991454206548</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01735445968235435</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.002985214909120795</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01064198499142273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>5079</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5845</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.005408753170758749</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.004521358995604</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1583; 11168</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4076</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2483; 13233</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.03816394775932227</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.01588584600961463</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02409483387260708</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +768,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.0123378004086516</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.008678044881606745</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.01060626187953974</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>8635</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5454</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14089</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.006277824861681523</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.003849373409413243</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.006805403385854466</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>4394; 16081</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2419; 10719</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9040; 23271</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02297678214419805</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.01705573606890976</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.01751878950197652</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +833,445 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>448</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>2453</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>657</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1838</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>563</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>2254</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>5160</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>6083</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2899</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2402</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>5301</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>677</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>696</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>7256</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>6436</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>10667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5079</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>766</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>5845</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1583</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>11168</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>4076</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>13233</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>8635</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>5454</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>14089</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>4394</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>2419</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>9040</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>16081</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>10719</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>23271</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>